--- a/Design Work/HHC/Prelim HHC BOM.xlsx
+++ b/Design Work/HHC/Prelim HHC BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nate\Downloads\Cathode Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PerytonElectricPropulsion\Design Work\HHC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACE8997-9C76-4A13-B719-9DB7D1D3E321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D97D9-B702-4A67-AB9C-D6E5EBDF7D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FBC354F0-549C-4B23-AB67-491F45504AF1}"/>
   </bookViews>
@@ -469,18 +469,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9AF862-C870-4A4E-92EE-F0EC8A6F7476}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -491,12 +491,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -506,8 +506,9 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -518,7 +519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -528,8 +529,9 @@
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -540,22 +542,22 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/Design Work/HHC/Prelim HHC BOM.xlsx
+++ b/Design Work/HHC/Prelim HHC BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PerytonElectricPropulsion\Design Work\HHC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94D97D9-B702-4A67-AB9C-D6E5EBDF7D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF9FA19-B0B6-4FF2-9273-F0066946C375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{FBC354F0-549C-4B23-AB67-491F45504AF1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Heaterless Hollow Cathode Preliminary BOM</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Insert (HCA125 insert, need to email to clarify on buying insert by itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.par-direct.co.uk/product-details/INBD/WEB-MP-1200X1000 </t>
+  </si>
+  <si>
+    <t>.3mm thickness is better for bending and wrapping</t>
   </si>
 </sst>
 </file>
@@ -469,18 +475,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9AF862-C870-4A4E-92EE-F0EC8A6F7476}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -491,12 +497,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -508,7 +514,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -519,7 +525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -531,7 +537,7 @@
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -541,23 +547,29 @@
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -568,6 +580,7 @@
     <hyperlink ref="C6" r:id="rId2" display="https://products.swagelok.com/en/c/jam-nuts/p/SS-812-61" xr:uid="{F75ED361-D3DC-49C2-8708-B0E66CA1DC11}"/>
     <hyperlink ref="C7" r:id="rId3" display="https://uk.rs-online.com/web/p/plastic-film/7850827" xr:uid="{7325D7EF-25EF-4D29-971B-229CE5DB2F89}"/>
     <hyperlink ref="C5" r:id="rId4" display="https://shop.plasmacontrols.com/collections/cathode-tips-without-heaters/products/hca125-cathode-assembly?variant=46362306347195" xr:uid="{6134CBE4-20D4-48A5-B254-E2E19106F543}"/>
+    <hyperlink ref="I7" r:id="rId5" tooltip="https://www.par-direct.co.uk/product-details/INBD/WEB-MP-1200X1000" display="https://www.par-direct.co.uk/product-details/INBD/WEB-MP-1200X1000" xr:uid="{EB92C151-23BA-4F41-A70D-4A1A09810597}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
